--- a/SustitucionMOA/Documentacion/TemplatePrecargaSolp.xlsx
+++ b/SustitucionMOA/Documentacion/TemplatePrecargaSolp.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartin\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFCC3D36-0C91-4B4D-B008-79915E518C20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EC610D-35A6-4E88-BE83-C6DF1DE17D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10110" yWindow="-12630" windowWidth="22430" windowHeight="11030" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1040" yWindow="-13360" windowWidth="22430" windowHeight="11030" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -28,6 +28,7 @@
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author/>
+    <author>Eugenio Martin</author>
   </authors>
   <commentList>
     <comment ref="N1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
@@ -147,6 +148,54 @@
             <charset val="1"/>
           </rPr>
           <t>Para servicios refiere a la subposición, para materiales al material</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="S1" authorId="1" shapeId="0" xr:uid="{4A615EC0-5F49-47B5-B52F-D4F4417266E5}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Eugenio Martin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Solo para material no catalogado</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="T1" authorId="1" shapeId="0" xr:uid="{F38A6632-7E0F-4730-82EE-D2792808157A}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>Eugenio Martin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Solo para material no catalogado</t>
         </r>
       </text>
     </comment>
@@ -155,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>Nro posición</t>
   </si>
@@ -218,13 +267,19 @@
   </si>
   <si>
     <t>Precio</t>
+  </si>
+  <si>
+    <t>Motivo</t>
+  </si>
+  <si>
+    <t>Modelo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -244,6 +299,19 @@
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -725,7 +793,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R11"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.140625" customWidth="1"/>
@@ -739,7 +807,7 @@
     <col min="20" max="20" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -794,25 +862,31 @@
       <c r="R1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="S1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="T1" s="3" t="s">
+        <v>22</v>
+      </c>
     </row>
-    <row r="2" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:18" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:18" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="6" t="s">
         <v>17</v>
       </c>

--- a/SustitucionMOA/Documentacion/TemplatePrecargaSolp.xlsx
+++ b/SustitucionMOA/Documentacion/TemplatePrecargaSolp.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartin\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emartin\source\repos\WebOperaciones\SustitucionMOA\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26EC610D-35A6-4E88-BE83-C6DF1DE17D6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93ECA71F-3C88-4529-B240-8BA4B3BE000D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1040" yWindow="-13360" windowWidth="22430" windowHeight="11030" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-14510" windowWidth="34620" windowHeight="13900" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>Nro posición</t>
   </si>
@@ -273,6 +273,9 @@
   </si>
   <si>
     <t>Modelo</t>
+  </si>
+  <si>
+    <t>Solicitante</t>
   </si>
 </sst>
 </file>
@@ -793,7 +796,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:U11"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.5703125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.140625" customWidth="1"/>
@@ -807,7 +810,7 @@
     <col min="20" max="20" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" ht="45" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -868,25 +871,28 @@
       <c r="T1" s="3" t="s">
         <v>22</v>
       </c>
+      <c r="U1" s="2" t="s">
+        <v>23</v>
+      </c>
     </row>
-    <row r="2" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="8" spans="1:20" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="11" spans="1:20" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="8" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="1:21" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="L11" s="6" t="s">
         <v>17</v>
       </c>
